--- a/output/pdf_financials_xlsx/NRED.xlsx
+++ b/output/pdf_financials_xlsx/NRED.xlsx
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.026581</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0.143877</v>
@@ -4242,7 +4242,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NRED.xlsx
+++ b/output/pdf_financials_xlsx/NRED.xlsx
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.024441</v>
+        <v>0.100229</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.000818</v>
+        <v>0.078559</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.050232</v>
+        <v>0.16492</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.07059799999999999</v>
+        <v>0.124138</v>
       </c>
     </row>
     <row r="11">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.024441</v>
+        <v>-0.100229</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.000818</v>
+        <v>-0.078559</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-0.16492</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000325</v>
       </c>
     </row>
     <row r="13">
@@ -951,7 +951,7 @@
         <v>-0.16492</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.29269</v>
+        <v>-0.293015</v>
       </c>
     </row>
     <row r="28">
@@ -989,7 +989,7 @@
         <v>-0.16492</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.29269</v>
+        <v>-0.293015</v>
       </c>
     </row>
     <row r="30">
@@ -1079,16 +1079,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.204525</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.098137</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.102594</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.477065</v>
       </c>
     </row>
     <row r="35">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.204525</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.098137</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.102594</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.477065</v>
       </c>
     </row>
     <row r="37">
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.236258</v>
+        <v>0.031733</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.132494</v>
+        <v>0.034357</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.116279</v>
+        <v>0.013685</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.531603</v>
+        <v>0.054538</v>
       </c>
     </row>
     <row r="49">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
